--- a/מודל_חיתום_פליפ_אינדיאנפוליס.xlsx
+++ b/מודל_חיתום_פליפ_אינדיאנפוליס.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מזומן_מול_מינוף" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -628,7 +628,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>מדיאן הזיפ × ~1.18 — לאמת מול 3 קומפס משופצים</t>
+          <t>קלט. מ-python3 arv.py comps / listings.py: ARV ÷ sqft. המכפיל 1.18 נפסל (decisions.md 6.9.2026)</t>
         </is>
       </c>
     </row>
@@ -872,8 +872,13 @@
         </is>
       </c>
       <c r="B31" s="15">
-        <f>12/B30</f>
-        <v/>
+        <f>12/(B30+1.5)</f>
+        <v/>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>+1.5 ח' חיפוש וסגירה של העסקה הבאה (~45 יום). היה 12/B30</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1179,11 +1184,11 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 46.2% מהעסקאות במאי 2026. Redfin לא מפרסמת גודל — הנעלם הגדול</t>
+          <t>נמדד 6.9.2026 מ-E3_Seller_Points, 9,736 מכירות: חציון 1.9%, p75 2.8%. לחיתום שמרני 2.8%</t>
         </is>
       </c>
     </row>
@@ -1321,18 +1326,23 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>הצעה מקסימלית — כלל ה-70%</t>
+          <t>הצעה מקסימלית — כלל ה-72%</t>
         </is>
       </c>
       <c r="B76" s="10">
-        <f>B8*0.7-B17</f>
-        <v/>
+        <f>B8*0.72-B17</f>
+        <v/>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>72% לקונה מזומן (decisions.md 6.9.2026). היה 70%</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>המחיר עומד בכלל ה-70%?</t>
+          <t>המחיר עומד בכלל ה-72%?</t>
         </is>
       </c>
       <c r="B77" s="20">
@@ -1755,7 +1765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2332,7 +2342,7 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>מעל הטווח</t>
+          <t>BUY BOX צפון</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
@@ -2434,7 +2444,7 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY BOX צפון</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
@@ -2587,7 +2597,7 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY BOX צפון</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
@@ -2689,7 +2699,7 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY BOX צפון</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
@@ -3568,6 +3578,13 @@
       <c r="A42" s="34" t="inlineStr">
         <is>
           <t>⚠️ מכירה של $250K-$350K במריון קאונטי דורשת 1,800-2,200 sqft, לא 1,400.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>🟢 6.9.2026: 46220/46205/46260/46240 נוספו כשכבה צפונית אחרי בדיקה עמוקה (docs/בדיקה_זיפים_צפוניים.md). מדד מכירות חוזרות של אותו בית +3.5%-5.3% בשנה; הסימון WATCH על $/sqft של Redfin היה תמהיל.</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4254,12 +4271,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>לא ידוע</t>
+          <t>חציון $5,000-6,500 · 1.9% מהמחיר · p75 2.8%</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>46.2% מהעסקאות במאי 2026. Redfin לא מפרסמת. הפריט הגדול ביותר שלא כומת</t>
+          <t>נמדד 6.9.2026 מ-E3_Seller_Points (9,736 מכירות 2024-26). ⚠️ שכיחות 25% בטופס מול 46% ב-Redfin — רצפה</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4322,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>הערכה שלי</t>
+          <t>נפסל — קומפס גאוגרפיים</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>לאמת מול 3 קומפס משופצים בכל זיפ לפני הצעה</t>
+          <t>arv.py: 10 קומפס, קונה תופס, שומה ±25%. שגיאה חציונית 12.4%, p90 42% (backtest 6.9.2026). הטווח הוא המוצר</t>
         </is>
       </c>
     </row>
@@ -4362,6 +4379,23 @@
       <c r="C30" s="37" t="inlineStr">
         <is>
           <t>אינדי לא מופיעה באף אחת מ-5 רשימות Q1 2026. נדרש מנוי</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>כלל ההצעה</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>72% (היה 70%)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>70% מכויל לקונה ממונף; במזומן חוזרות 2 נקודות ולא יותר. decisions.md 6.9.2026</t>
         </is>
       </c>
     </row>

--- a/מודל_חיתום_פליפ_אינדיאנפוליס.xlsx
+++ b/מודל_חיתום_פליפ_אינדיאנפוליס.xlsx
@@ -1326,23 +1326,23 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>הצעה מקסימלית — כלל ה-72%</t>
+          <t>הצעה מקסימלית — כלל ההצעה (72% · צפון 69%)</t>
         </is>
       </c>
       <c r="B76" s="10">
-        <f>B8*0.72-B17</f>
+        <f>B8*IF(OR(B4="46220",B4="46205",B4="46260",B4="46240"),0.69,0.72)-B17</f>
         <v/>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>72% לקונה מזומן (decisions.md 6.9.2026). היה 70%</t>
+          <t>לפי הזיפ בתא B4: BUY BOX 72%, צפון 69% (שגיאת ARV 18.7% שם). decisions.md 6.9.2026. היה 70%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>המחיר עומד בכלל ה-72%?</t>
+          <t>המחיר עומד בכלל ההצעה?</t>
         </is>
       </c>
       <c r="B77" s="20">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>72% (היה 70%)</t>
+          <t>72% ב-BUY BOX · 69% בצפון (היה 70%)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>70% מכויל לקונה ממונף; במזומן חוזרות 2 נקודות ולא יותר. decisions.md 6.9.2026</t>
+          <t>70% מכויל לקונה ממונף; במזומן חוזרות 2 נקודות. בצפון שגיאת ARV 18.7% ⇒ 69% לאותה כרית. decisions.md 6.9.2026</t>
         </is>
       </c>
     </row>
